--- a/04_DESIGN_TABLES/DesignTable_1700.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1700.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,26 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>COLLARD@DRIVE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>FLATL@DRIVE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>NECKD@DRIVE</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1237,24 +1257,49 @@
           <t>1700-20-16</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>1700-20-16</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); A16 round collar + two flats as Brennan (COLLARD / FLATL / NECKD from the own STEP)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1265,6 +1310,20 @@
       <c r="N16" t="inlineStr">
         <is>
           <t>1700-20-16</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1274,24 +1333,49 @@
           <t>1700-24-20</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>1700-24-20</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); bore: Brennan stepped 1.312 (JIC side) / 1.078 (flange side), modelled as one 1.078 through bore; A16 round collar + two flats as Brennan (COLLARD / FLATL / NECKD from the own STEP)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1302,6 +1386,20 @@
       <c r="N17" t="inlineStr">
         <is>
           <t>1700-24-20</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1311,24 +1409,49 @@
           <t>1700-32-24</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.622</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>1700-32-24</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); bore: Brennan stepped 1.781 (JIC side) / 1.5 (flange side), modelled as one 1.5 through bore; A16 round collar + two flats as Brennan (COLLARD / FLATL / NECKD from the own STEP)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1339,6 +1462,20 @@
       <c r="N18" t="inlineStr">
         <is>
           <t>1700-32-24</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
